--- a/data/knowledge_base/栢博材料询价登记表_三列_含本批追加.xlsx
+++ b/data/knowledge_base/栢博材料询价登记表_三列_含本批追加.xlsx
@@ -11668,7 +11668,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>14元/码²</t>
+          <t>8元/码</t>
         </is>
       </c>
     </row>
